--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617100</v>
+        <v>122617388</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593157</v>
+        <v>593062</v>
       </c>
       <c r="R2" t="n">
-        <v>6375469</v>
+        <v>6375611</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617388</v>
+        <v>122617100</v>
       </c>
       <c r="B3" t="n">
-        <v>95009</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,50 +808,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593062</v>
+        <v>593157</v>
       </c>
       <c r="R3" t="n">
-        <v>6375611</v>
+        <v>6375469</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
         <v>122617190</v>
       </c>
       <c r="B4" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617100</v>
+        <v>122617190</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +808,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593157</v>
+        <v>593162</v>
       </c>
       <c r="R3" t="n">
-        <v>6375469</v>
+        <v>6375524</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617190</v>
+        <v>122617100</v>
       </c>
       <c r="B4" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,50 +929,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593162</v>
+        <v>593157</v>
       </c>
       <c r="R4" t="n">
-        <v>6375524</v>
+        <v>6375469</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617388</v>
+        <v>122617190</v>
       </c>
       <c r="B2" t="n">
-        <v>95011</v>
+        <v>100507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593062</v>
+        <v>593162</v>
       </c>
       <c r="R2" t="n">
-        <v>6375611</v>
+        <v>6375524</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617190</v>
+        <v>122617388</v>
       </c>
       <c r="B3" t="n">
-        <v>100506</v>
+        <v>95012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593162</v>
+        <v>593062</v>
       </c>
       <c r="R3" t="n">
-        <v>6375524</v>
+        <v>6375611</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
         <v>122617100</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617190</v>
+        <v>122617388</v>
       </c>
       <c r="B3" t="n">
-        <v>100613</v>
+        <v>95126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,26 +803,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593162</v>
+        <v>593062</v>
       </c>
       <c r="R3" t="n">
-        <v>6375524</v>
+        <v>6375611</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617388</v>
+        <v>122617190</v>
       </c>
       <c r="B4" t="n">
-        <v>95118</v>
+        <v>100621</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593062</v>
+        <v>593162</v>
       </c>
       <c r="R4" t="n">
-        <v>6375611</v>
+        <v>6375524</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617100</v>
+        <v>122617388</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>95126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593157</v>
+        <v>593062</v>
       </c>
       <c r="R2" t="n">
-        <v>6375469</v>
+        <v>6375611</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617388</v>
+        <v>122617190</v>
       </c>
       <c r="B3" t="n">
-        <v>95126</v>
+        <v>100621</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593062</v>
+        <v>593162</v>
       </c>
       <c r="R3" t="n">
-        <v>6375611</v>
+        <v>6375524</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617190</v>
+        <v>122617100</v>
       </c>
       <c r="B4" t="n">
-        <v>100621</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,50 +929,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593162</v>
+        <v>593157</v>
       </c>
       <c r="R4" t="n">
-        <v>6375524</v>
+        <v>6375469</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617388</v>
+        <v>122617100</v>
       </c>
       <c r="B2" t="n">
-        <v>95126</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593062</v>
+        <v>593157</v>
       </c>
       <c r="R2" t="n">
-        <v>6375611</v>
+        <v>6375469</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617190</v>
+        <v>122617388</v>
       </c>
       <c r="B3" t="n">
-        <v>100621</v>
+        <v>95128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +803,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593162</v>
+        <v>593062</v>
       </c>
       <c r="R3" t="n">
-        <v>6375524</v>
+        <v>6375611</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617100</v>
+        <v>122617190</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>100623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,41 +920,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593157</v>
+        <v>593162</v>
       </c>
       <c r="R4" t="n">
-        <v>6375469</v>
+        <v>6375524</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617100</v>
+        <v>122617190</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>100631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593157</v>
+        <v>593162</v>
       </c>
       <c r="R2" t="n">
-        <v>6375469</v>
+        <v>6375524</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617388</v>
+        <v>122617100</v>
       </c>
       <c r="B3" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,50 +808,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593062</v>
+        <v>593157</v>
       </c>
       <c r="R3" t="n">
-        <v>6375611</v>
+        <v>6375469</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617190</v>
+        <v>122617388</v>
       </c>
       <c r="B4" t="n">
-        <v>100623</v>
+        <v>95136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593162</v>
+        <v>593062</v>
       </c>
       <c r="R4" t="n">
-        <v>6375524</v>
+        <v>6375611</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617190</v>
+        <v>122617100</v>
       </c>
       <c r="B2" t="n">
-        <v>100631</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593162</v>
+        <v>593157</v>
       </c>
       <c r="R2" t="n">
-        <v>6375524</v>
+        <v>6375469</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617100</v>
+        <v>122617190</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>100631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593157</v>
+        <v>593162</v>
       </c>
       <c r="R3" t="n">
-        <v>6375469</v>
+        <v>6375524</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,419 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123283794</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95136</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nymossen, Nymossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593162</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6375437</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123284099</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95136</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nymossen, Nymossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593046</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6375595</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123283959</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95136</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nymossen, Nymossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>593061</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6375612</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123283787</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43822</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Logmossen, Logmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593219</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6375367</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283794</v>
+        <v>123283787</v>
       </c>
       <c r="B5" t="n">
-        <v>95136</v>
+        <v>43822</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,37 +1045,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>101735</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nymossen, Nymossen, Sm</t>
+          <t>Logmossen, Logmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593162</v>
+        <v>593219</v>
       </c>
       <c r="R5" t="n">
-        <v>6375437</v>
+        <v>6375367</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,12 +1099,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,19 +1124,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284099</v>
+        <v>123283959</v>
       </c>
       <c r="B6" t="n">
         <v>95136</v>
@@ -1171,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593046</v>
+        <v>593061</v>
       </c>
       <c r="R6" t="n">
-        <v>6375595</v>
+        <v>6375612</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,19 +1226,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123283959</v>
+        <v>123284099</v>
       </c>
       <c r="B7" t="n">
         <v>95136</v>
@@ -1273,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593061</v>
+        <v>593046</v>
       </c>
       <c r="R7" t="n">
-        <v>6375612</v>
+        <v>6375595</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,22 +1328,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123283787</v>
+        <v>123283794</v>
       </c>
       <c r="B8" t="n">
-        <v>43822</v>
+        <v>95136</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,37 +1356,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Logmossen, Logmossen, Sm</t>
+          <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593219</v>
+        <v>593162</v>
       </c>
       <c r="R8" t="n">
-        <v>6375367</v>
+        <v>6375437</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,17 +1410,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,12 +1430,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283787</v>
+        <v>123284099</v>
       </c>
       <c r="B5" t="n">
-        <v>43822</v>
+        <v>95139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,37 +1045,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Logmossen, Logmossen, Sm</t>
+          <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593219</v>
+        <v>593046</v>
       </c>
       <c r="R5" t="n">
-        <v>6375367</v>
+        <v>6375595</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,17 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1134,7 @@
         <v>123283959</v>
       </c>
       <c r="B6" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1238,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284099</v>
+        <v>123283794</v>
       </c>
       <c r="B7" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593046</v>
+        <v>593162</v>
       </c>
       <c r="R7" t="n">
-        <v>6375595</v>
+        <v>6375437</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,22 +1323,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123283794</v>
+        <v>123283787</v>
       </c>
       <c r="B8" t="n">
-        <v>95136</v>
+        <v>43825</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,37 +1351,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>101735</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nymossen, Nymossen, Sm</t>
+          <t>Logmossen, Logmossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593162</v>
+        <v>593219</v>
       </c>
       <c r="R8" t="n">
-        <v>6375437</v>
+        <v>6375367</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,12 +1405,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,12 +1430,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>123284099</v>
       </c>
       <c r="B5" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>123283959</v>
       </c>
       <c r="B6" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>123283794</v>
       </c>
       <c r="B7" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284099</v>
+        <v>123283787</v>
       </c>
       <c r="B5" t="n">
-        <v>95141</v>
+        <v>43825</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,37 +1045,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>101735</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nymossen, Nymossen, Sm</t>
+          <t>Logmossen, Logmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593046</v>
+        <v>593219</v>
       </c>
       <c r="R5" t="n">
-        <v>6375595</v>
+        <v>6375367</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,12 +1099,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283959</v>
+        <v>123284099</v>
       </c>
       <c r="B6" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593061</v>
+        <v>593046</v>
       </c>
       <c r="R6" t="n">
-        <v>6375612</v>
+        <v>6375595</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,12 +1226,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1236,7 +1241,7 @@
         <v>123283794</v>
       </c>
       <c r="B7" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123283787</v>
+        <v>123283959</v>
       </c>
       <c r="B8" t="n">
-        <v>43825</v>
+        <v>95147</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,37 +1356,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Logmossen, Logmossen, Sm</t>
+          <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593219</v>
+        <v>593061</v>
       </c>
       <c r="R8" t="n">
-        <v>6375367</v>
+        <v>6375612</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,17 +1410,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,12 +1430,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>123283959</v>
       </c>
       <c r="B5" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284099</v>
+        <v>123283787</v>
       </c>
       <c r="B6" t="n">
-        <v>95150</v>
+        <v>43831</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,37 +1147,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>101735</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nymossen, Nymossen, Sm</t>
+          <t>Logmossen, Logmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593046</v>
+        <v>593219</v>
       </c>
       <c r="R6" t="n">
-        <v>6375595</v>
+        <v>6375367</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,12 +1201,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123283787</v>
+        <v>123284099</v>
       </c>
       <c r="B7" t="n">
-        <v>43825</v>
+        <v>95167</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,37 +1254,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Logmossen, Logmossen, Sm</t>
+          <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593219</v>
+        <v>593046</v>
       </c>
       <c r="R7" t="n">
-        <v>6375367</v>
+        <v>6375595</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,17 +1308,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1343,7 @@
         <v>123283794</v>
       </c>
       <c r="B8" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284099</v>
+        <v>123283794</v>
       </c>
       <c r="B7" t="n">
         <v>95167</v>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593046</v>
+        <v>593162</v>
       </c>
       <c r="R7" t="n">
-        <v>6375595</v>
+        <v>6375437</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,19 +1328,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123283794</v>
+        <v>123284099</v>
       </c>
       <c r="B8" t="n">
         <v>95167</v>
@@ -1380,13 +1380,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593162</v>
+        <v>593046</v>
       </c>
       <c r="R8" t="n">
-        <v>6375437</v>
+        <v>6375595</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,12 +1430,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283959</v>
+        <v>123284099</v>
       </c>
       <c r="B5" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593061</v>
+        <v>593046</v>
       </c>
       <c r="R5" t="n">
-        <v>6375612</v>
+        <v>6375595</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283787</v>
+        <v>123283959</v>
       </c>
       <c r="B6" t="n">
-        <v>43831</v>
+        <v>95173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,37 +1147,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Logmossen, Logmossen, Sm</t>
+          <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593219</v>
+        <v>593061</v>
       </c>
       <c r="R6" t="n">
-        <v>6375367</v>
+        <v>6375612</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,17 +1201,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,12 +1221,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1241,7 +1236,7 @@
         <v>123283794</v>
       </c>
       <c r="B7" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123284099</v>
+        <v>123283787</v>
       </c>
       <c r="B8" t="n">
-        <v>95167</v>
+        <v>43834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,37 +1351,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>101735</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nymossen, Nymossen, Sm</t>
+          <t>Logmossen, Logmossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593046</v>
+        <v>593219</v>
       </c>
       <c r="R8" t="n">
-        <v>6375595</v>
+        <v>6375367</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,12 +1418,18 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284099</v>
+        <v>123283959</v>
       </c>
       <c r="B5" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593046</v>
+        <v>593061</v>
       </c>
       <c r="R5" t="n">
-        <v>6375595</v>
+        <v>6375612</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283959</v>
+        <v>123284099</v>
       </c>
       <c r="B6" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593061</v>
+        <v>593046</v>
       </c>
       <c r="R6" t="n">
-        <v>6375612</v>
+        <v>6375595</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,12 +1221,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>123283794</v>
       </c>
       <c r="B7" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283959</v>
+        <v>123284099</v>
       </c>
       <c r="B5" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593061</v>
+        <v>593046</v>
       </c>
       <c r="R5" t="n">
-        <v>6375612</v>
+        <v>6375595</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284099</v>
+        <v>123283959</v>
       </c>
       <c r="B6" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593046</v>
+        <v>593061</v>
       </c>
       <c r="R6" t="n">
-        <v>6375595</v>
+        <v>6375612</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,12 +1221,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>123283794</v>
       </c>
       <c r="B7" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284099</v>
+        <v>123283959</v>
       </c>
       <c r="B5" t="n">
         <v>95683</v>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593046</v>
+        <v>593061</v>
       </c>
       <c r="R5" t="n">
-        <v>6375595</v>
+        <v>6375612</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283959</v>
+        <v>123283794</v>
       </c>
       <c r="B6" t="n">
         <v>95683</v>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593061</v>
+        <v>593162</v>
       </c>
       <c r="R6" t="n">
-        <v>6375612</v>
+        <v>6375437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123283794</v>
+        <v>123284099</v>
       </c>
       <c r="B7" t="n">
         <v>95683</v>
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593162</v>
+        <v>593046</v>
       </c>
       <c r="R7" t="n">
-        <v>6375437</v>
+        <v>6375595</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283959</v>
+        <v>123283794</v>
       </c>
       <c r="B5" t="n">
         <v>95683</v>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593061</v>
+        <v>593162</v>
       </c>
       <c r="R5" t="n">
-        <v>6375612</v>
+        <v>6375437</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283794</v>
+        <v>123283959</v>
       </c>
       <c r="B6" t="n">
         <v>95683</v>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593162</v>
+        <v>593061</v>
       </c>
       <c r="R6" t="n">
-        <v>6375437</v>
+        <v>6375612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283794</v>
+        <v>123283959</v>
       </c>
       <c r="B5" t="n">
         <v>95683</v>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593162</v>
+        <v>593061</v>
       </c>
       <c r="R5" t="n">
-        <v>6375437</v>
+        <v>6375612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283959</v>
+        <v>123283794</v>
       </c>
       <c r="B6" t="n">
         <v>95683</v>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593061</v>
+        <v>593162</v>
       </c>
       <c r="R6" t="n">
-        <v>6375612</v>
+        <v>6375437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617100</v>
+        <v>122617388</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593157</v>
+        <v>593062</v>
       </c>
       <c r="R2" t="n">
-        <v>6375469</v>
+        <v>6375611</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617190</v>
+        <v>123283794</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,33 +802,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
@@ -839,10 +829,10 @@
         <v>593162</v>
       </c>
       <c r="R3" t="n">
-        <v>6375524</v>
+        <v>6375437</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,27 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617388</v>
+        <v>123283959</v>
       </c>
       <c r="B4" t="n">
-        <v>95136</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,29 +916,20 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593062</v>
+        <v>593061</v>
       </c>
       <c r="R4" t="n">
-        <v>6375611</v>
+        <v>6375612</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,27 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283959</v>
+        <v>123284099</v>
       </c>
       <c r="B5" t="n">
-        <v>95683</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,13 +1020,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593061</v>
+        <v>593046</v>
       </c>
       <c r="R5" t="n">
-        <v>6375612</v>
+        <v>6375595</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,65 +1070,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283794</v>
+        <v>123284245</v>
       </c>
       <c r="B6" t="n">
-        <v>95683</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nymossen, Nymossen, Sm</t>
+          <t>Smedgölen, Smedgölen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593162</v>
+        <v>593019</v>
       </c>
       <c r="R6" t="n">
-        <v>6375437</v>
+        <v>6375614</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,15 +1179,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284099</v>
+        <v>122617100</v>
       </c>
       <c r="B7" t="n">
-        <v>95683</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,21 +1190,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,13 +1214,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593046</v>
+        <v>593157</v>
       </c>
       <c r="R7" t="n">
-        <v>6375595</v>
+        <v>6375469</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1244,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,12 +1274,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1338,12 +1289,7 @@
         <v>123283787</v>
       </c>
       <c r="B8" t="n">
-        <v>43834</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,6 +1392,122 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122617190</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nymossen, Nymossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>593162</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6375524</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7029-2025 artfynd.xlsx
+++ b/artfynd/A 7029-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122617388</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283794</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283959</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284099</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284245</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122617100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283787</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,8 +1547,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122617190</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>